--- a/Clientes/SQES/000002 - 20260318_Caso_3612471 Modificar 4 exportaciones para agregar Empresa/Documentación/CuadroIntegraciones_.xlsx
+++ b/Clientes/SQES/000002 - 20260318_Caso_3612471 Modificar 4 exportaciones para agregar Empresa/Documentación/CuadroIntegraciones_.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Clientes\Meta4_Global\Clientes\SQES\000002 - 20260318_Caso_XXXXXXXX DESCRIPCION\Documentación\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Clientes\Meta4_Global\Clientes\SQES\000002 - 20260318_Caso_3612471 Modificar 4 exportaciones para agregar Empresa\Documentación\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF78040B-6DCC-41DC-A632-8A4C033ADCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7319786F-E143-4287-9C54-0A63C5082F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88034E7E-4DDC-4FE0-AA32-01EE34A8BD3E}"/>
   </bookViews>
